--- a/dentai-web/selenium-tests/reports/05_dental_scan_report.xlsx
+++ b/dentai-web/selenium-tests/reports/05_dental_scan_report.xlsx
@@ -443,7 +443,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:41:17 am</v>
+        <v>6/8/2026, 9:57:19 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -498,7 +498,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>1.47 seconds</v>
+        <v>1.50 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -639,10 +639,10 @@
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:11:17.970Z</v>
+        <v>2026-08-06T04:27:19.462Z</v>
       </c>
       <c r="H2" t="str">
         <v>N/A</v>
@@ -659,16 +659,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D3" t="str">
-        <v>WEB-SEL-202: File File Picker Upload Button Interaction</v>
+        <v>WEB-SEL-202: File Picker Upload Button Interaction Click</v>
       </c>
       <c r="E3" t="str">
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H3" t="str">
         <v>N/A</v>
@@ -691,10 +691,10 @@
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H4" t="str">
         <v>N/A</v>
@@ -717,10 +717,10 @@
         <v>PASS</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H5" t="str">
         <v>N/A</v>
@@ -746,7 +746,7 @@
         <v>43</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H6" t="str">
         <v>N/A</v>
@@ -769,10 +769,10 @@
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H7" t="str">
         <v>N/A</v>
@@ -789,16 +789,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D8" t="str">
-        <v>WEB-SEL-207: Crop Image Tool Adjustment Handles</v>
+        <v>WEB-SEL-207: Crop Image Tool Adjustment Handles Test</v>
       </c>
       <c r="E8" t="str">
         <v>PASS</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H8" t="str">
         <v>N/A</v>
@@ -821,10 +821,10 @@
         <v>PASS</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H9" t="str">
         <v>N/A</v>
@@ -847,10 +847,10 @@
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H10" t="str">
         <v>N/A</v>
@@ -873,10 +873,10 @@
         <v>PASS</v>
       </c>
       <c r="F11">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H11" t="str">
         <v>N/A</v>
@@ -893,16 +893,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D12" t="str">
-        <v>WEB-SEL-211: Tartar / Plaque Coverage Highlights</v>
+        <v>WEB-SEL-211: Tartar / Plaque Coverage Highlights Layer</v>
       </c>
       <c r="E12" t="str">
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H12" t="str">
         <v>N/A</v>
@@ -919,16 +919,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D13" t="str">
-        <v>WEB-SEL-212: Gingivitis Inflammation Color Layer</v>
+        <v>WEB-SEL-212: Gingivitis Inflammation Color Layer Toggle</v>
       </c>
       <c r="E13" t="str">
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H13" t="str">
         <v>N/A</v>
@@ -945,16 +945,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D14" t="str">
-        <v>WEB-SEL-213: Enamel Crack Line Marking Annotations</v>
+        <v>WEB-SEL-213: Enamel Crack Line Marking Annotations View</v>
       </c>
       <c r="E14" t="str">
         <v>PASS</v>
       </c>
       <c r="F14">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H14" t="str">
         <v>N/A</v>
@@ -977,10 +977,10 @@
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H15" t="str">
         <v>N/A</v>
@@ -1003,10 +1003,10 @@
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H16" t="str">
         <v>N/A</v>
@@ -1029,10 +1029,10 @@
         <v>PASS</v>
       </c>
       <c r="F17">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H17" t="str">
         <v>N/A</v>
@@ -1055,10 +1055,10 @@
         <v>PASS</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H18" t="str">
         <v>N/A</v>
@@ -1081,10 +1081,10 @@
         <v>PASS</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H19" t="str">
         <v>N/A</v>
@@ -1101,16 +1101,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D20" t="str">
-        <v>WEB-SEL-219: Export Annotated Radiograph Image</v>
+        <v>WEB-SEL-219: Export Annotated Radiograph Image File</v>
       </c>
       <c r="E20" t="str">
         <v>PASS</v>
       </c>
       <c r="F20">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H20" t="str">
         <v>N/A</v>
@@ -1133,10 +1133,10 @@
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H21" t="str">
         <v>N/A</v>
@@ -1159,10 +1159,10 @@
         <v>PASS</v>
       </c>
       <c r="F22">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H22" t="str">
         <v>N/A</v>
@@ -1185,10 +1185,10 @@
         <v>PASS</v>
       </c>
       <c r="F23">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H23" t="str">
         <v>N/A</v>
@@ -1211,10 +1211,10 @@
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H24" t="str">
         <v>N/A</v>
@@ -1237,10 +1237,10 @@
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H25" t="str">
         <v>N/A</v>
@@ -1263,10 +1263,10 @@
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H26" t="str">
         <v>N/A</v>
@@ -1283,16 +1283,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D27" t="str">
-        <v>WEB-SEL-226: Tooth FDI Numbering Overlay Toggle</v>
+        <v>WEB-SEL-226: Tooth FDI Numbering Overlay Toggle Switch</v>
       </c>
       <c r="E27" t="str">
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H27" t="str">
         <v>N/A</v>
@@ -1315,10 +1315,10 @@
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H28" t="str">
         <v>N/A</v>
@@ -1341,10 +1341,10 @@
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H29" t="str">
         <v>N/A</v>
@@ -1367,10 +1367,10 @@
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H30" t="str">
         <v>N/A</v>
@@ -1393,10 +1393,10 @@
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H31" t="str">
         <v>N/A</v>
@@ -1413,16 +1413,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D32" t="str">
-        <v>WEB-SEL-231: Incisor View Camera Mode Selection</v>
+        <v>WEB-SEL-231: Incisor View Camera Mode Selection Button</v>
       </c>
       <c r="E32" t="str">
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H32" t="str">
         <v>N/A</v>
@@ -1439,16 +1439,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D33" t="str">
-        <v>WEB-SEL-232: Molar View Camera Mode Selection</v>
+        <v>WEB-SEL-232: Molar View Camera Mode Selection Button</v>
       </c>
       <c r="E33" t="str">
         <v>PASS</v>
       </c>
       <c r="F33">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H33" t="str">
         <v>N/A</v>
@@ -1471,10 +1471,10 @@
         <v>PASS</v>
       </c>
       <c r="F34">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H34" t="str">
         <v>N/A</v>
@@ -1497,10 +1497,10 @@
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H35" t="str">
         <v>N/A</v>
@@ -1517,16 +1517,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D36" t="str">
-        <v>WEB-SEL-235: 3D CBCT Scan Volume Slice Navigator</v>
+        <v>WEB-SEL-235: 3D CBCT Scan Volume Slice Navigator Drag</v>
       </c>
       <c r="E36" t="str">
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H36" t="str">
         <v>N/A</v>
@@ -1549,10 +1549,10 @@
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H37" t="str">
         <v>N/A</v>
@@ -1569,16 +1569,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D38" t="str">
-        <v>WEB-SEL-237: Magnifying Glass Lens Hover Tool</v>
+        <v>WEB-SEL-237: Magnifying Glass Lens Hover Tool Component</v>
       </c>
       <c r="E38" t="str">
         <v>PASS</v>
       </c>
       <c r="F38">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H38" t="str">
         <v>N/A</v>
@@ -1595,16 +1595,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D39" t="str">
-        <v>WEB-SEL-238: Add Custom Clinical Annotation Note</v>
+        <v>WEB-SEL-238: Add Custom Clinical Annotation Note Pin</v>
       </c>
       <c r="E39" t="str">
         <v>PASS</v>
       </c>
       <c r="F39">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H39" t="str">
         <v>N/A</v>
@@ -1621,16 +1621,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D40" t="str">
-        <v>WEB-SEL-239: Save Scan to Patient Record Library</v>
+        <v>WEB-SEL-239: Save Scan to Patient Record Library Album</v>
       </c>
       <c r="E40" t="str">
         <v>PASS</v>
       </c>
       <c r="F40">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H40" t="str">
         <v>N/A</v>
@@ -1653,10 +1653,10 @@
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H41" t="str">
         <v>N/A</v>
@@ -1673,16 +1673,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D42" t="str">
-        <v>WEB-SEL-241: Filter Saved Scans by Date Range</v>
+        <v>WEB-SEL-241: Filter Saved Scans by Date Range Picker</v>
       </c>
       <c r="E42" t="str">
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H42" t="str">
         <v>N/A</v>
@@ -1705,10 +1705,10 @@
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H43" t="str">
         <v>N/A</v>
@@ -1725,16 +1725,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D44" t="str">
-        <v>WEB-SEL-243: Print Scan Summary Sheet Action</v>
+        <v>WEB-SEL-243: Print Scan Summary Sheet Action Trigger</v>
       </c>
       <c r="E44" t="str">
         <v>PASS</v>
       </c>
       <c r="F44">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H44" t="str">
         <v>N/A</v>
@@ -1751,16 +1751,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D45" t="str">
-        <v>WEB-SEL-244: AI Model Architecture Info Drawer</v>
+        <v>WEB-SEL-244: AI Model Architecture Info Drawer View</v>
       </c>
       <c r="E45" t="str">
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H45" t="str">
         <v>N/A</v>
@@ -1783,10 +1783,10 @@
         <v>PASS</v>
       </c>
       <c r="F46">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H46" t="str">
         <v>N/A</v>
@@ -1809,10 +1809,10 @@
         <v>PASS</v>
       </c>
       <c r="F47">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H47" t="str">
         <v>N/A</v>
@@ -1835,10 +1835,10 @@
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H48" t="str">
         <v>N/A</v>
@@ -1855,16 +1855,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D49" t="str">
-        <v>WEB-SEL-248: Batch Processing Queue Progress Bar</v>
+        <v>WEB-SEL-248: Batch Processing Queue Progress Bar View</v>
       </c>
       <c r="E49" t="str">
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H49" t="str">
         <v>N/A</v>
@@ -1887,10 +1887,10 @@
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H50" t="str">
         <v>N/A</v>
@@ -1907,16 +1907,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D51" t="str">
-        <v>WEB-SEL-250: Interactive 3D Tooth Model Sync View</v>
+        <v>WEB-SEL-250: Interactive 3D Tooth Model Sync View Render</v>
       </c>
       <c r="E51" t="str">
         <v>PASS</v>
       </c>
       <c r="F51">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H51" t="str">
         <v>N/A</v>
@@ -1979,10 +1979,10 @@
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.970Z</v>
+        <v>2026-08-06T04:27:19.462Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -1996,16 +1996,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C3" t="str">
-        <v>WEB-SEL-202: File File Picker Upload Button Interaction</v>
+        <v>WEB-SEL-202: File Picker Upload Button Interaction Click</v>
       </c>
       <c r="D3" t="str">
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -2025,10 +2025,10 @@
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -2048,10 +2048,10 @@
         <v>PASS</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -2074,7 +2074,7 @@
         <v>43</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -2094,10 +2094,10 @@
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -2111,16 +2111,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C8" t="str">
-        <v>WEB-SEL-207: Crop Image Tool Adjustment Handles</v>
+        <v>WEB-SEL-207: Crop Image Tool Adjustment Handles Test</v>
       </c>
       <c r="D8" t="str">
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -2140,10 +2140,10 @@
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -2163,10 +2163,10 @@
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -2186,10 +2186,10 @@
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -2203,16 +2203,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C12" t="str">
-        <v>WEB-SEL-211: Tartar / Plaque Coverage Highlights</v>
+        <v>WEB-SEL-211: Tartar / Plaque Coverage Highlights Layer</v>
       </c>
       <c r="D12" t="str">
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -2226,16 +2226,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C13" t="str">
-        <v>WEB-SEL-212: Gingivitis Inflammation Color Layer</v>
+        <v>WEB-SEL-212: Gingivitis Inflammation Color Layer Toggle</v>
       </c>
       <c r="D13" t="str">
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -2249,16 +2249,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C14" t="str">
-        <v>WEB-SEL-213: Enamel Crack Line Marking Annotations</v>
+        <v>WEB-SEL-213: Enamel Crack Line Marking Annotations View</v>
       </c>
       <c r="D14" t="str">
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -2278,10 +2278,10 @@
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -2301,10 +2301,10 @@
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -2324,10 +2324,10 @@
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -2347,10 +2347,10 @@
         <v>PASS</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -2370,10 +2370,10 @@
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -2387,16 +2387,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C20" t="str">
-        <v>WEB-SEL-219: Export Annotated Radiograph Image</v>
+        <v>WEB-SEL-219: Export Annotated Radiograph Image File</v>
       </c>
       <c r="D20" t="str">
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -2416,10 +2416,10 @@
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -2439,10 +2439,10 @@
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -2462,10 +2462,10 @@
         <v>PASS</v>
       </c>
       <c r="E23">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -2485,10 +2485,10 @@
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -2508,10 +2508,10 @@
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -2531,10 +2531,10 @@
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -2548,16 +2548,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C27" t="str">
-        <v>WEB-SEL-226: Tooth FDI Numbering Overlay Toggle</v>
+        <v>WEB-SEL-226: Tooth FDI Numbering Overlay Toggle Switch</v>
       </c>
       <c r="D27" t="str">
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -2577,10 +2577,10 @@
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -2600,10 +2600,10 @@
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -2623,10 +2623,10 @@
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -2646,10 +2646,10 @@
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -2663,16 +2663,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C32" t="str">
-        <v>WEB-SEL-231: Incisor View Camera Mode Selection</v>
+        <v>WEB-SEL-231: Incisor View Camera Mode Selection Button</v>
       </c>
       <c r="D32" t="str">
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -2686,16 +2686,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C33" t="str">
-        <v>WEB-SEL-232: Molar View Camera Mode Selection</v>
+        <v>WEB-SEL-232: Molar View Camera Mode Selection Button</v>
       </c>
       <c r="D33" t="str">
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -2715,10 +2715,10 @@
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -2738,10 +2738,10 @@
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -2755,16 +2755,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C36" t="str">
-        <v>WEB-SEL-235: 3D CBCT Scan Volume Slice Navigator</v>
+        <v>WEB-SEL-235: 3D CBCT Scan Volume Slice Navigator Drag</v>
       </c>
       <c r="D36" t="str">
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -2784,10 +2784,10 @@
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -2801,16 +2801,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C38" t="str">
-        <v>WEB-SEL-237: Magnifying Glass Lens Hover Tool</v>
+        <v>WEB-SEL-237: Magnifying Glass Lens Hover Tool Component</v>
       </c>
       <c r="D38" t="str">
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -2824,16 +2824,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C39" t="str">
-        <v>WEB-SEL-238: Add Custom Clinical Annotation Note</v>
+        <v>WEB-SEL-238: Add Custom Clinical Annotation Note Pin</v>
       </c>
       <c r="D39" t="str">
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -2847,16 +2847,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C40" t="str">
-        <v>WEB-SEL-239: Save Scan to Patient Record Library</v>
+        <v>WEB-SEL-239: Save Scan to Patient Record Library Album</v>
       </c>
       <c r="D40" t="str">
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -2876,10 +2876,10 @@
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -2893,16 +2893,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-241: Filter Saved Scans by Date Range</v>
+        <v>WEB-SEL-241: Filter Saved Scans by Date Range Picker</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -2922,10 +2922,10 @@
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -2939,16 +2939,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C44" t="str">
-        <v>WEB-SEL-243: Print Scan Summary Sheet Action</v>
+        <v>WEB-SEL-243: Print Scan Summary Sheet Action Trigger</v>
       </c>
       <c r="D44" t="str">
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -2962,16 +2962,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C45" t="str">
-        <v>WEB-SEL-244: AI Model Architecture Info Drawer</v>
+        <v>WEB-SEL-244: AI Model Architecture Info Drawer View</v>
       </c>
       <c r="D45" t="str">
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -2991,10 +2991,10 @@
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -3014,10 +3014,10 @@
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -3037,10 +3037,10 @@
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -3054,16 +3054,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C49" t="str">
-        <v>WEB-SEL-248: Batch Processing Queue Progress Bar</v>
+        <v>WEB-SEL-248: Batch Processing Queue Progress Bar View</v>
       </c>
       <c r="D49" t="str">
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -3083,10 +3083,10 @@
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -3100,16 +3100,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C51" t="str">
-        <v>WEB-SEL-250: Interactive 3D Tooth Model Sync View</v>
+        <v>WEB-SEL-250: Interactive 3D Tooth Model Sync View Render</v>
       </c>
       <c r="D51" t="str">
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>
